--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 11/02. Trả bảo hành/TBH_.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 11/02. Trả bảo hành/TBH_.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\02. Trả bảo hành\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 11\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4131B20-101D-4C74-88D4-DE56F13A7D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5049DF47-9EC4-4BF8-8410-E336BF6B4845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,12 +131,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="13"/>
       <color theme="1"/>
@@ -144,17 +138,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,14 +145,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <color theme="1"/>
@@ -177,26 +152,58 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -369,167 +376,167 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="17"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="18"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="18"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="12"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="18"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="12"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="17"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -562,7 +569,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>1025769</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>67060</xdr:rowOff>
+      <xdr:rowOff>103695</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -911,341 +918,341 @@
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="46" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="47" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="49"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="50" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="53" t="s">
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="59"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="55"/>
-    </row>
-    <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="62"/>
+    </row>
+    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="60" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="63" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="36"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="42" t="s">
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="41" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="38"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="34"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="40"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="31"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="40"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="31"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="40"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="31"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="34"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="46"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="19"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="50"/>
     </row>
     <row r="26" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
     </row>
     <row r="65" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
